--- a/171/food/2026-01-27-sm.xlsx
+++ b/171/food/2026-01-27-sm.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>27.01.2026</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Каша рисовая с изюмом</t>
+          <t>Каша рисовая с изюмом №177</t>
         </is>
       </c>
       <c r="E4" s="21" t="n">
@@ -984,7 +984,7 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Чай с молоком или сливками</t>
+          <t>Чай с молоком или сливками №378</t>
         </is>
       </c>
       <c r="E6" s="29" t="n">
@@ -1013,11 +1013,7 @@
           <t>хлеб</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
+      <c r="C7" s="26" t="e"/>
       <c r="D7" s="25" t="inlineStr">
         <is>
           <t>Хлеб пшеничный</t>
@@ -1056,7 +1052,7 @@
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>Яблоко</t>
+          <t>Яблоко №338</t>
         </is>
       </c>
       <c r="E8" s="29" t="n">
@@ -1129,14 +1125,34 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="C12" s="26" t="e"/>
-      <c r="D12" s="25" t="e"/>
-      <c r="E12" s="27" t="e"/>
-      <c r="F12" s="27" t="e"/>
-      <c r="G12" s="27" t="e"/>
-      <c r="H12" s="27" t="e"/>
-      <c r="I12" s="27" t="e"/>
-      <c r="J12" s="28" t="e"/>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Суп-пюре из картофеля №131</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>200</v>
+      </c>
+      <c r="F12" s="32" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="G12" s="43" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="H12" s="43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I12" s="43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J12" s="44" t="n">
+        <v>13.7</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="24" t="e"/>
@@ -1146,13 +1162,29 @@
         </is>
       </c>
       <c r="C13" s="26" t="e"/>
-      <c r="D13" s="25" t="e"/>
-      <c r="E13" s="27" t="e"/>
-      <c r="F13" s="27" t="e"/>
-      <c r="G13" s="27" t="e"/>
-      <c r="H13" s="27" t="e"/>
-      <c r="I13" s="27" t="e"/>
-      <c r="J13" s="28" t="e"/>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Сосиски "Особые халяль"</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>90</v>
+      </c>
+      <c r="F13" s="32" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="G13" s="43" t="n">
+        <v>153.4</v>
+      </c>
+      <c r="H13" s="43" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I13" s="43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J13" s="44" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="24" t="e"/>
@@ -1161,14 +1193,34 @@
           <t>гарнир</t>
         </is>
       </c>
-      <c r="C14" s="26" t="e"/>
-      <c r="D14" s="25" t="e"/>
-      <c r="E14" s="27" t="e"/>
-      <c r="F14" s="27" t="e"/>
-      <c r="G14" s="27" t="e"/>
-      <c r="H14" s="27" t="e"/>
-      <c r="I14" s="27" t="e"/>
-      <c r="J14" s="28" t="e"/>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>Рис отварной №304</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>150</v>
+      </c>
+      <c r="F14" s="32" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="G14" s="29" t="n">
+        <v>214</v>
+      </c>
+      <c r="H14" s="43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I14" s="43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J14" s="44" t="n">
+        <v>36.7</v>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="24" t="e"/>
@@ -1177,14 +1229,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="C15" s="26" t="e"/>
-      <c r="D15" s="25" t="e"/>
-      <c r="E15" s="27" t="e"/>
-      <c r="F15" s="27" t="e"/>
-      <c r="G15" s="27" t="e"/>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>180</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G15" s="43" t="n">
+        <v>35.1</v>
+      </c>
       <c r="H15" s="27" t="e"/>
-      <c r="I15" s="27" t="e"/>
-      <c r="J15" s="28" t="e"/>
+      <c r="I15" s="43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J15" s="44" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="24" t="e"/>
@@ -1194,13 +1264,29 @@
         </is>
       </c>
       <c r="C16" s="26" t="e"/>
-      <c r="D16" s="25" t="e"/>
-      <c r="E16" s="27" t="e"/>
-      <c r="F16" s="27" t="e"/>
-      <c r="G16" s="27" t="e"/>
-      <c r="H16" s="27" t="e"/>
-      <c r="I16" s="27" t="e"/>
-      <c r="J16" s="28" t="e"/>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="E16" s="29" t="n">
+        <v>80</v>
+      </c>
+      <c r="F16" s="32" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="G16" s="29" t="n">
+        <v>187</v>
+      </c>
+      <c r="H16" s="43" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I16" s="43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J16" s="44" t="n">
+        <v>38.6</v>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="24" t="e"/>
